--- a/AAII_Financials/Quarterly/SNA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>SNA</t>
   </si>
@@ -656,538 +656,550 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E7" s="2">
         <v>46116</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46025</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44198</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1334800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1308300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1339900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1291900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1281100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1243200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1299200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1247400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1279900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1281900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1293800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1254200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1284700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1275600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1244200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1189800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1223000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1185500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1195200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1125000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1168300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1113200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1167800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1027400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>808900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>938100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1039100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>985900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1035400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1007300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1035200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>980100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1036600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1018500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1054500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>982800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>999100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>963900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>964000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>905700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>599900</v>
+      </c>
+      <c r="E9" s="3">
         <v>598900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>626400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>584900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>583900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>562600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>602600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>559200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>582100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>585600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>619000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>581100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>587600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>593400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>619600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>590800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>604200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>580800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>594600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>517000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>538300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>511000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>557300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>471400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>378000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>425500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>504700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>453700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>477500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>450100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>495100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>444200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>467500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>463900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>509300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>455200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>458400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>439100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>445900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>415000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>702700</v>
+      </c>
+      <c r="E10" s="3">
         <v>676300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>680000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>674900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>663700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>648800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>662900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>659500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>667500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>665000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>645500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>647700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>670600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>655900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>624600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>599000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>618800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>604700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>600600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>608000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>630000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>602200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>610500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>556000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>430900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>512600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>534400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>532200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>557900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>557200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>540100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>535900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>569100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>554600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>545200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>527600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>540700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>524800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>518100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>490700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1230,19 +1242,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>72400</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1250,11 +1263,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>67000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1262,11 +1275,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>64700</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1352,8 +1365,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1474,40 +1490,43 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-22000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>11200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-11300</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1521,11 +1540,11 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1539,24 +1558,24 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>3800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>7800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1564,11 +1583,11 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-11600</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1576,10 +1595,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>7800</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
@@ -1596,53 +1615,56 @@
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E15" s="3">
         <v>25000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>24000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>24600</v>
       </c>
       <c r="K15" s="3">
         <v>24600</v>
       </c>
       <c r="L15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="M15" s="3">
         <v>24500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>24800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>24900</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1718,8 +1740,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1759,252 +1784,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>995800</v>
+      </c>
+      <c r="E17" s="3">
         <v>986900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>999600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>965600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>953200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>928900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>960600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>916500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>911800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>947000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>958600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>930100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>931600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>939900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>932300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>899900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>911100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>892000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>895800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>853100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>882300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>847000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>883100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>776100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>660200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>742300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>805500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>757200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>784900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>757800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>797000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>747700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>785700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>791700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>842400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>773700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>760800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>741900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>736300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>697500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>339000</v>
+      </c>
+      <c r="E18" s="3">
         <v>321400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>340300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>326300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>327900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>314300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>338600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>330900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>368100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>334900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>335200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>324100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>353100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>335700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>311900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>289900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>311900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>293500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>299400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>271900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>286000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>266200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>284700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>251300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>148700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>195800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>233600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>228700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>250500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>249500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>238200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>232400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>250900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>226800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>212100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>209100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>238300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>222000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>227700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>208200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2047,618 +2079,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
       </c>
       <c r="H20" s="3">
         <v>400</v>
       </c>
       <c r="I20" s="3">
+        <v>400</v>
+      </c>
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>11800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>13100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>9300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>10600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>362400</v>
+      </c>
+      <c r="E21" s="3">
         <v>346600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>353200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>349500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>351900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>337900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>350400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>354100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>390800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>357600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>346400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>346300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>375600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>358200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>348400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>327400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>346600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>327500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>334200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>300500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>314900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>295200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>312300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>278000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>174500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>221100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>259900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>254400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>275600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>273600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>264100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>254600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>274300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>261400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>234400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>230500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>259200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>243400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>249100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>228600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E22" s="3">
         <v>12400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>12500</v>
       </c>
       <c r="M22" s="3">
         <v>12500</v>
       </c>
       <c r="N22" s="3">
+        <v>12500</v>
+      </c>
+      <c r="O22" s="3">
         <v>12400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>14300</v>
       </c>
       <c r="X22" s="3">
         <v>14300</v>
       </c>
       <c r="Y22" s="3">
+        <v>14300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>15400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12500</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>12400</v>
       </c>
       <c r="AH22" s="3">
         <v>12400</v>
       </c>
       <c r="AI22" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>12000</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>13600</v>
       </c>
       <c r="AK22" s="3">
         <v>13600</v>
       </c>
       <c r="AL22" s="3">
+        <v>13600</v>
+      </c>
+      <c r="AM22" s="3">
         <v>13100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>13000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>12700</v>
-      </c>
-      <c r="AO22" s="3">
-        <v>13100</v>
       </c>
       <c r="AP22" s="3">
         <v>13100</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>13100</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>339200</v>
+      </c>
+      <c r="E23" s="3">
         <v>323200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>341900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>349300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>329300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>315400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>339200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>332200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>356900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>344800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>330800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>320200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>348100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>328900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>311700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>291200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>309500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>290200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>293200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>262400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>275100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>256200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>271700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>240300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>137300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>185900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>223900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>219500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>240200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>238500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>228800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>219000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>238300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>223800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>197000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>193900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>223400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>207600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>214300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>194300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E24" s="3">
         <v>69700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>74900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>77500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>72500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>68700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>75000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>74700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>79300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>75200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>69500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>71100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>78200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>74600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>67200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>61700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>72300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>67500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>64100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>60900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>62900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>59100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>58200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>55100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>31900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>43900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>48900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>50400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>55600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>56900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>49500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>49700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>56300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>55000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>56800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>57200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>67300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>62600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>64900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>59600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2779,252 +2827,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>266200</v>
+      </c>
+      <c r="E26" s="3">
         <v>253500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>267000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>271800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>256800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>246700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>264200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>257500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>277600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>269600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>261300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>249100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>269900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>254300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>244500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>229500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>237200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>222700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>229100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>201500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>212200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>197100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>213500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>185200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>105400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>142000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>175000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>169100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>184600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>181600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>179300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>169300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>182000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>168800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>140200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>136700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>156100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>145000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>149400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>134700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E27" s="3">
         <v>247000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>260700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>265400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>250300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>240500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>258100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>251100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>271200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>263500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>255300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>243100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>264000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>248700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>238900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>223900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>231500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>217400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>223700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>196200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>208000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>192600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>208900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>179700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>101200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>137200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>170600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>164600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>180400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>177900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>175000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>165000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>178200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>165600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>136500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>133400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>153200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>141600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>146300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3145,8 +3202,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3222,8 +3282,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3237,23 +3297,23 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>500</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-7000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3267,8 +3327,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3389,8 +3452,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3511,252 +3577,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
       </c>
       <c r="H32" s="3">
         <v>-400</v>
       </c>
       <c r="I32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-11800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-13100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-9300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-10600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E33" s="3">
         <v>247000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>260700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>265400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>250300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>240500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>258100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>251100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>271200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>263500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>255300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>243100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>264000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>248700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>238900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>223900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>231500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>217400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>223700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>196200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>208000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>192600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>208900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>179700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>101200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>137200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>170600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>164600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>180400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>177900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>175000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>163200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>178700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>163000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>129500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>133400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>153200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>141600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>146300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3877,257 +3952,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E35" s="3">
         <v>247000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>260700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>265400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>250300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>240500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>258100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>251100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>271200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>263500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>255300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>243100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>264000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>248700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>238900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>223900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>231500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>217400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>223700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>196200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>208000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>192600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>208900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>179700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>101200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>137200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>170600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>164600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>180400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>177900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>175000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>163200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>178700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>163000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>129500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>133400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>153200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>141600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>146300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E38" s="2">
         <v>46116</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46025</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44198</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4170,8 +4254,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4214,130 +4299,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1644200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1752800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1624100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1533900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1458200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1434700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1360400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1313200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1232600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1120900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1001300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>959100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>871100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>833400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>757200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>759300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>812900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>861100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>780000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>735500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>965900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>904600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>923400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>787500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>686200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>185800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>184500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>167500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>164000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>156400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>140900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>122200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>112300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>97500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>92000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>94100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>89000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>123000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>77600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>117500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4434,287 +4523,296 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>8</v>
+      <c r="AI42" s="3">
+        <v>0</v>
       </c>
       <c r="AJ42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AK42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL42" s="3">
         <v>21900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>26500</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>28400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>23900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>22300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>18800</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>945500</v>
+      </c>
+      <c r="E43" s="3">
         <v>894000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>885100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>929800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>846300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>856300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>819800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>800500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>787600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>831800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>796100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>781700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>791700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>787000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1433800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1409800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1374400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1376100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1335000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1315800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1284600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1286200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1283400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1264300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1169700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1241700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1325400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1321000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1304600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1294100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1309400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1303300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1269100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1285000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1277800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1280800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1224200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1177300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1159400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1156200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1045300</v>
+      </c>
+      <c r="E44" s="3">
         <v>1020500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1025200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1024500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>997700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>961200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>943400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>995800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>965000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>970500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1005900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1032900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1046100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1049100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1033100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>955100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>893300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>864100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>803800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>789600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>760900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>730100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>746500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>764400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>784000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>757400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>760400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>753500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>725800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>707000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>673800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>690600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>668300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>678800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>638800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>649900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>601400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>556800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>530500</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>523600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>33100</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -4722,11 +4820,11 @@
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>35700</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
@@ -4734,11 +4832,11 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>37800</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
@@ -4746,208 +4844,214 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>144800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>145400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>150100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>134700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>134600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>133400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>138300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>131600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>129700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>122000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>132500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>118200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>110200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>105900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>112200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>107800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>92800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>98500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>107100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>88800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>94600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>91100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>93100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>94200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>92600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4523700</v>
+      </c>
+      <c r="E46" s="3">
         <v>4547700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4402800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4385300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4219600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4141400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3989400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4000700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3858100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3776100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3652000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3605000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3533400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3481200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3368900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3269600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3230700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3236000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3053400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2974300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3149700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3052500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3083000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2938200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2772400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2303100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2380500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2347900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2306600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2265300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2216900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2214600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2155400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2168400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2119300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2145900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2034100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1974100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1884000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1908700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4990,330 +5094,339 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>1554600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1505300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1502400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1476800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1492200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1490500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1504300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1492300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1511000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1489500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1507200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1457300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1463600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1433300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1436500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1422200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1419300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1396400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1383900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1362000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1380400</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1347400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1315400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1274700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1236400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1199600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>562600</v>
+      </c>
+      <c r="E48" s="3">
         <v>629900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>628200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>646900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>647900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>633900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>624000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>626300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>613600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>605800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>610300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>593500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>591800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>573800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>574100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>542100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>560100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>563200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>570100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>573800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>578500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>569000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>578100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>556400</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>559600</v>
       </c>
       <c r="AB48" s="3">
         <v>559600</v>
       </c>
       <c r="AC48" s="3">
+        <v>559600</v>
+      </c>
+      <c r="AD48" s="3">
         <v>577100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>564200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>561800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>552400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>495100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>491000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>479400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>489700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>484400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>474200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>463400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>437500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>425200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>419200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1499300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1369300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1380200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1381200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1377700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1349100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1324400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1363900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1342700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1349000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1366300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1298900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1318100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1323900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1320900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1281900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1329500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1373300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1418200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1420600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1432800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1416400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1243200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1180100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1165500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1132500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1157700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1145300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1134900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1131400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1135100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1151700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1151900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1193100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1177800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1182300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1155500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1100200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1080100</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>973800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5434,8 +5547,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5556,130 +5672,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>199400</v>
+      </c>
+      <c r="E52" s="3">
         <v>196600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>198900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>154200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>148500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>144400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>142700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>151600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>147800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>150000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>144500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>85500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>86600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>84700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>154300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>236600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>241600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>245900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>225800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>121700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>126300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>143300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>142000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>103400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>108800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>111800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>114600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>105700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>105600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>119600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>106700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>101100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>101400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>104400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>87200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>106400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>98700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>91300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>97500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>98800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5800,130 +5922,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8640900</v>
+      </c>
+      <c r="E54" s="3">
         <v>8516400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8412300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8355600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8201800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8069000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7896800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7953300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7759900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7666800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7544900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7304300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7230400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7125600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6972800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6835500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6864300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6895200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6759700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6580900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6791600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6673500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6557300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6267600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6113500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5564300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5693500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5596400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5545400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5490900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5373100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5354800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5272000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5317600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5249100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5256200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5067100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4877800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>4723200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>4600100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5966,8 +6094,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6010,740 +6139,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E57" s="3">
         <v>252000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>227600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>269700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>267400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>279800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>265400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>268800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>270200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>256700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>236200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>283300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>273100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>283100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>287000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>305300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>308500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>297300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>277600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>266900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>280200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>235900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>222900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>206000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>186200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>193700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>198500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>205800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>215300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>200400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>201100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>197600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>198500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>188200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>178200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>204700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>202300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>189900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>170900</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>172600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>346800</v>
+      </c>
+      <c r="E58" s="3">
         <v>344500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>49500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>44800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>39200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>41000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>40400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>40300</v>
       </c>
       <c r="O58" s="3">
         <v>40300</v>
       </c>
       <c r="P58" s="3">
+        <v>40300</v>
+      </c>
+      <c r="Q58" s="3">
         <v>39500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>19200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>19600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>20900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21900</v>
-      </c>
-      <c r="U58" s="3">
-        <v>19800</v>
       </c>
       <c r="V58" s="3">
         <v>19800</v>
       </c>
       <c r="W58" s="3">
+        <v>19800</v>
+      </c>
+      <c r="X58" s="3">
         <v>270700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>271100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>271200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>270600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>162900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>205700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>235200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>169700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>142500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>186300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>164500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>127600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>145200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>433200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>453400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>350200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>267200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>301400</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>182600</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E59" s="3">
         <v>64400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>205600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>73800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>72100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>71100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>220400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>79200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>76800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>73700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>226100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>76000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>73700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>72500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>665400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>668600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>656700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>704900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>684800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>693000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>671200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>727100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>670800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>640400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>628200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>565300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>543400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>549100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>545800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>593100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>564600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>594700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>600900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>618200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>581900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>564700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>521300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>514400</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>517200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>523400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1317900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1289100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>918500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>996800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>941500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>999900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>961500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>956400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>950100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>989700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>941600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>981900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>962300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>999000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>971600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>993500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>986100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1024100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>982200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>979700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1222100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1234100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1164900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1117000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>829400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>921900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>947600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>990100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>930800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>936000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>952000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>956800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>927000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>951600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1193300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1222800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1073800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>971500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>989500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>878600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E61" s="3">
         <v>68800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>62800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>65700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>68600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>71100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>58100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>55800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>55400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>55700</v>
-      </c>
-      <c r="N61" s="3">
-        <v>51800</v>
       </c>
       <c r="O61" s="3">
         <v>51800</v>
       </c>
       <c r="P61" s="3">
+        <v>51800</v>
+      </c>
+      <c r="Q61" s="3">
         <v>46500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1185700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1185900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1186300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1186900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1187400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1187900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1188200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1188800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1189500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1190000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1445600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>957300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>956900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>958300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>955000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>953600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>946000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>944800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>945400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>946300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>753600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>755000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>755600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>755400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>708800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>713400</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E62" s="3">
         <v>96800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>97400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>95900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>92100</v>
       </c>
       <c r="H62" s="3">
         <v>92100</v>
       </c>
       <c r="I62" s="3">
+        <v>92100</v>
+      </c>
+      <c r="J62" s="3">
         <v>91900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>86900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>85800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>88700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>86300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>81500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>85600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>82800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>312000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>316600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>345100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>363600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>386300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>344000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>355800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>352700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>356300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>319800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>329900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>331700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>358200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>322800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>350900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>383500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>356500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>269100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>288000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>317400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>329900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>338400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>364700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>385100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>389700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>319500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6864,8 +7012,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6986,8 +7137,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7108,130 +7262,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2574600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2533300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2455500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2511800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2462300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2524900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2479800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2455600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2451000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2503500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2451500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2451900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2451100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2493200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2491500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2518300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2539900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2596900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2577800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2533600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2788200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2797500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2732400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2648600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2626800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2233000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2284400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2292600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2257300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2293300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2274300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2190400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2178800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2233700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2295200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2334400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2212200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2130100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2106000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1929500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7274,8 +7434,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7396,8 +7557,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7518,8 +7682,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7640,8 +7807,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7762,130 +7932,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8391100</v>
+      </c>
+      <c r="E72" s="3">
         <v>8257400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8137500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8003900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7850500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7712400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7584300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7439000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7286000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7113100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6948500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6792300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6635600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6458100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6296200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6144000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5996200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5841000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5699900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5552800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5423500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5282500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5156900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5014900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4894200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4852000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4779700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4668300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4556100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4428400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4257600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4135800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4018900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3886700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3772300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3689500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3597000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3485200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3384900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3280000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8006,8 +8182,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8128,8 +8307,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8250,130 +8432,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6041300</v>
+      </c>
+      <c r="E76" s="3">
         <v>5958100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5931800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5819000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5715500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5520800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5394100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5475000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5286300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5141000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5071300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4830200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4757100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4610200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4481300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4317200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4324400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4298300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4181900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4047300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4003400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3876000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3824900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3619000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3486700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3331300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3409100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3303800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3288100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3197600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3098800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3164400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3093200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3083900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2953900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2921800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2854900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2747700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2617200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2670600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8494,257 +8682,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E80" s="2">
         <v>46116</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46025</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44198</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>260600</v>
+      </c>
+      <c r="E81" s="3">
         <v>247000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>260700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>265400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>250300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>240500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>258100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>251100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>271200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>263500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>255300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>243100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>264000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>248700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>238900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>223900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>231500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>217400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>223700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>196200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>208000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>192600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>208900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>179700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>101200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>137200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>170600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>164600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>180400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>177900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>175000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>163200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>178700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>163000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>129500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>133400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>153200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>141600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>146300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>131700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8787,130 +8984,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E83" s="3">
         <v>18300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>18200</v>
       </c>
       <c r="H83" s="3">
         <v>18200</v>
       </c>
       <c r="I83" s="3">
+        <v>18200</v>
+      </c>
+      <c r="J83" s="3">
         <v>14500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>17800</v>
       </c>
       <c r="K83" s="3">
         <v>17800</v>
       </c>
       <c r="L83" s="3">
+        <v>17800</v>
+      </c>
+      <c r="M83" s="3">
         <v>18000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>18200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>18500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>25400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>25700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>24900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>25500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>24700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>25200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>23900</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>23800</v>
       </c>
       <c r="AB83" s="3">
         <v>23800</v>
       </c>
       <c r="AC83" s="3">
+        <v>23800</v>
+      </c>
+      <c r="AD83" s="3">
         <v>23900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>22900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>23000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>22900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>23200</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>24000</v>
       </c>
       <c r="AJ83" s="3">
         <v>24000</v>
       </c>
       <c r="AK83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="AL83" s="3">
         <v>23800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>23500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>22800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>23100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>21700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9031,8 +9232,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9153,8 +9357,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9275,8 +9482,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9397,8 +9607,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9519,130 +9732,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>271500</v>
+      </c>
+      <c r="E89" s="3">
         <v>368700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>268100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>277900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>237200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>298500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>293500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>274200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>301100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>348700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>296900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>285400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>270300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>301600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>210600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>129900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>140800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>193900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>222700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>186400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>238200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>319300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>317600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>224000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>253600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>213400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>196700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>131100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>145500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>201300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>215900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>129800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>186900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>231900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>193500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>95500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>127100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>192400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>160500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>111900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9685,130 +9904,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-19700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-21100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-20000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-18300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-17200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-21600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-28000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-24700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-22900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-15800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-18600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9929,8 +10152,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10051,130 +10277,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-195100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-46000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-32000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-40200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-40500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-60200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-63200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-104600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-59700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-94600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-72900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-67900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-57900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-73800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23800</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-29700</v>
       </c>
       <c r="W94" s="3">
         <v>-29700</v>
       </c>
       <c r="X94" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-207200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-73600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-45600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-49800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-41400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-76800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-65200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-38700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-60800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-48600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-63700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-37100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-62100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-138600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-81700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-229300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-69200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10217,55 +10449,56 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>126400</v>
+      </c>
+      <c r="E96" s="3">
         <v>126800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>126700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>111500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>111800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>112200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>112300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>97900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>98000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>98200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>98000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>85600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>85900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>86100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-86000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-75700</v>
       </c>
       <c r="S96" s="3">
         <v>-75700</v>
@@ -10274,73 +10507,76 @@
         <v>-75700</v>
       </c>
       <c r="U96" s="3">
+        <v>-75700</v>
+      </c>
+      <c r="V96" s="3">
         <v>-76100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-66300</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-66700</v>
       </c>
       <c r="X96" s="3">
         <v>-66700</v>
       </c>
       <c r="Y96" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-66800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-58800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-58700</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-59000</v>
       </c>
       <c r="AC96" s="3">
         <v>-59000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-52300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-52500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-52800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-53100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-46100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-46300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-46500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-46400</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-40700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-41100</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-41200</v>
       </c>
       <c r="AO96" s="3">
         <v>-41200</v>
       </c>
       <c r="AP96" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-35400</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10461,8 +10697,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10583,8 +10822,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10705,370 +10947,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-185800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-211100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-204500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-180900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-170900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-193600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-201500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-156200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-127900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-164200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-149000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-135300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-136500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-152100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-145800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-120700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-112200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-106300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-154100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-385800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-147900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-131000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-111600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-105100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>289500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-157100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-139200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-49500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-73100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-147600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-135100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-71300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-105300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-190500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-136600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-29500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-23400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-66600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>30800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-44900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E101" s="3">
         <v>1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1700</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1200</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>1200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-108600</v>
+      </c>
+      <c r="E102" s="3">
         <v>128800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>90400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>75800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>23400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>74400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>47200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>80600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>111700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>119500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>42200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>88000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>37500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>76600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-53600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-48200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>81100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>44500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-230400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>61300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-18800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>135900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>101300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>500400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>17000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>7600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>15500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>18700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>9900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>14800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>5500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>5100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>45400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-39900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-2400</v>
       </c>
     </row>
